--- a/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-doanh-nghiep.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-doanh-nghiep.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\internlink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A7628B-7733-4BA9-BBBD-C4C8F3D0F007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740F116A-DEB4-4977-819C-6B467B166E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>Email</t>
   </si>
@@ -41,27 +41,6 @@
     <t>Website</t>
   </si>
   <si>
-    <t>FPT Software</t>
-  </si>
-  <si>
-    <t>Cong nghe thong tin</t>
-  </si>
-  <si>
-    <t>Ms. Linh Tran</t>
-  </si>
-  <si>
-    <t>linh.tran@fptsoftware.com</t>
-  </si>
-  <si>
-    <t>0909123456</t>
-  </si>
-  <si>
-    <t>Phu My Hung, Q7, TP.HCM</t>
-  </si>
-  <si>
-    <t>https://fptsoftware.com</t>
-  </si>
-  <si>
     <t>DANH SÁCH DOANH NGHIỆP LIÊN KẾT</t>
   </si>
   <si>
@@ -86,7 +65,61 @@
     <t>Số lượng tiếp nhận</t>
   </si>
   <si>
-    <t>Mã doanh nghiệp</t>
+    <t>Công ty TNHH FPT Software</t>
+  </si>
+  <si>
+    <t>Công nghệ thông tin</t>
+  </si>
+  <si>
+    <t>Mã DN</t>
+  </si>
+  <si>
+    <t>Mã Vị Trí</t>
+  </si>
+  <si>
+    <t>Tên vị trí tuyển dụng</t>
+  </si>
+  <si>
+    <t>Chuyên ngành yêu cầu</t>
+  </si>
+  <si>
+    <t>DN_FPT</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn HR</t>
+  </si>
+  <si>
+    <t>hr@fpt.com</t>
+  </si>
+  <si>
+    <t>TP. Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>https://fpt-software.com</t>
+  </si>
+  <si>
+    <t>VT_FPT_01</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>Công nghệ phần mềm</t>
+  </si>
+  <si>
+    <t>VT_FPT_02</t>
+  </si>
+  <si>
+    <t>Frontend Developer</t>
+  </si>
+  <si>
+    <t>VT_FPT_03</t>
+  </si>
+  <si>
+    <t>QA / Tester</t>
+  </si>
+  <si>
+    <t>02873000999</t>
   </si>
 </sst>
 </file>
@@ -162,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -170,6 +203,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -475,132 +513,210 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <f>IF(B3="","",1)</f>
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>12</v>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <f>IF(B4="","",A3+1)</f>
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="4">
         <v>3</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="4">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <f t="shared" ref="A5:A68" si="0">IF(B5="","",A4+1)</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="str">
-        <f>IF(B4="","",A3+1)</f>
-        <v/>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="str">
-        <f t="shared" ref="A5:A68" si="0">IF(B5="","",A4+1)</f>
-        <v/>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -610,12 +726,15 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -625,12 +744,15 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="6"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -640,12 +762,15 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="G8" s="6"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -655,12 +780,15 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="6"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -670,12 +798,15 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -685,12 +816,15 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -700,12 +834,15 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -715,12 +852,15 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -730,12 +870,15 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -745,12 +888,15 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -760,12 +906,15 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -775,12 +924,15 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="G17" s="6"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -790,12 +942,15 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -805,12 +960,15 @@
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -820,12 +978,15 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -835,12 +996,15 @@
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -850,12 +1014,15 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -865,12 +1032,15 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -880,12 +1050,15 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -895,12 +1068,15 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -910,12 +1086,15 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -925,12 +1104,15 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -940,12 +1122,15 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -955,12 +1140,15 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -970,12 +1158,15 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -985,12 +1176,15 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1000,12 +1194,15 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1015,12 +1212,15 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1030,12 +1230,15 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1045,12 +1248,15 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1060,12 +1266,15 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1075,12 +1284,15 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1090,12 +1302,15 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1105,12 +1320,15 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1120,12 +1338,15 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1135,12 +1356,15 @@
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1150,12 +1374,15 @@
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1165,12 +1392,15 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1180,12 +1410,15 @@
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1195,12 +1428,15 @@
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1210,12 +1446,15 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1225,12 +1464,15 @@
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1240,12 +1482,15 @@
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1255,12 +1500,15 @@
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1270,12 +1518,15 @@
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1285,12 +1536,15 @@
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1300,12 +1554,15 @@
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1315,12 +1572,15 @@
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1330,12 +1590,15 @@
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="G54" s="6"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1345,12 +1608,15 @@
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1360,12 +1626,15 @@
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1375,12 +1644,15 @@
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1390,12 +1662,15 @@
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
+      <c r="G58" s="6"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1405,12 +1680,15 @@
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1420,12 +1698,15 @@
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1435,12 +1716,15 @@
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1450,12 +1734,15 @@
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1465,12 +1752,15 @@
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
+      <c r="G63" s="6"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1480,12 +1770,15 @@
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="G64" s="6"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1495,12 +1788,15 @@
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1510,12 +1806,15 @@
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="G66" s="6"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1525,12 +1824,15 @@
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
+      <c r="G67" s="6"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1540,12 +1842,15 @@
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="G68" s="6"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="str">
         <f t="shared" ref="A69:A94" si="1">IF(B69="","",A68+1)</f>
         <v/>
@@ -1555,12 +1860,15 @@
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
+      <c r="G69" s="6"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1570,12 +1878,15 @@
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
+      <c r="G70" s="6"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1585,12 +1896,15 @@
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
+      <c r="G71" s="6"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1600,12 +1914,15 @@
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
+      <c r="G72" s="6"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1615,12 +1932,15 @@
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
+      <c r="G73" s="6"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1630,12 +1950,15 @@
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
+      <c r="G74" s="6"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1645,12 +1968,15 @@
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
+      <c r="G75" s="6"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1660,12 +1986,15 @@
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
+      <c r="G76" s="6"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1675,12 +2004,15 @@
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
+      <c r="G77" s="6"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1690,12 +2022,15 @@
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
+      <c r="G78" s="6"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1705,12 +2040,15 @@
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
+      <c r="G79" s="6"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1720,12 +2058,15 @@
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
+      <c r="G80" s="6"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1735,12 +2076,15 @@
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
+      <c r="G81" s="6"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1750,12 +2094,15 @@
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
+      <c r="G82" s="6"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1765,12 +2112,15 @@
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
+      <c r="G83" s="6"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1780,12 +2130,15 @@
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
+      <c r="G84" s="6"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1795,12 +2148,15 @@
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
+      <c r="G85" s="6"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1810,12 +2166,15 @@
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
+      <c r="G86" s="6"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1825,12 +2184,15 @@
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
+      <c r="G87" s="6"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1840,12 +2202,15 @@
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
+      <c r="G88" s="6"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1855,12 +2220,15 @@
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
+      <c r="G89" s="6"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1870,12 +2238,15 @@
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
+      <c r="G90" s="6"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1885,12 +2256,15 @@
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
+      <c r="G91" s="6"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1900,12 +2274,15 @@
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
+      <c r="G92" s="6"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1915,12 +2292,15 @@
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
+      <c r="G93" s="6"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1930,14 +2310,17 @@
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
+      <c r="G94" s="6"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
